--- a/artfynd/A 45917-2024 artfynd.xlsx
+++ b/artfynd/A 45917-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1992343</v>
+        <v>249750</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dottemålen, 450 meter NO, Sm</t>
+          <t>600 m NO Dottemålen (07E7f16), Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476657.9024182183</v>
+        <v>476685</v>
       </c>
       <c r="R2" t="n">
-        <v>6434074.031366067</v>
+        <v>6434078</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-08-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-02-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-08-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-02-13</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>lönnAntal: rikligt med stora bålarObservatör: Tomas Fasth</t>
+          <t>070475161 / BUXB VIR / Enstaka-sparsam (1)  / OBJ.AREA:0,2 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,23 +762,129 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>rasbrant</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1992343</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Dottemålen, 450 meter NO, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>476658</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6434074</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2005-08-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2005-08-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>lönnAntal: rikligt med stora bålarObservatör: Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>rasbrant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Anna Isaksson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Tomas Fasth</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45917-2024 artfynd.xlsx
+++ b/artfynd/A 45917-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/249750</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,8 +895,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1992343</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>